--- a/daily_matches/job_matches_2026-10-08.xlsx
+++ b/daily_matches/job_matches_2026-10-08.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,25 +456,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Customer Solution Architect — Arango AI Product Suite</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ARANGO</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.7</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Copilot, Hugging Face, FAISS, Pinecone, BigQuery, MLflow, FastAPI</t>
+          <t>RAG, Copilot, MLflow, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,32 +484,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d52bde6426b7b2e8</t>
+          <t>https://www.indeed.com/viewjob?jk=415b6d66e75228d2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer I</t>
+          <t>Platform Engineer Consultant</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FedEx Dataworks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Azure ML, Docker</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Pinecone, MLflow, Kubernetes, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,67 +519,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c1b2b06cb6b3d3</t>
+          <t>https://www.indeed.com/viewjob?jk=98d8a4cf8d1aaf1e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer I</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FedEx Dataworks</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.2</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Azure ML, Docker</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, scikit-learn, XGBoost, MLflow, CI/CD, Git, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4728a5662dc7585</t>
+          <t>https://www.indeed.com/viewjob?jk=21725d4d5a969dd0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer I</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FedEx Dataworks</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>22.2</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Azure ML, Docker</t>
+          <t>AWS SageMaker, Glue, Redshift, BigQuery, Synapse, Data Lake, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,67 +589,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad6553285bc3649a</t>
+          <t>https://www.indeed.com/viewjob?jk=ca5dc654cacc73fe</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI/ML Engineering Intern</t>
+          <t>Senior Applied AI-Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Novacis Digital</t>
+          <t>Atlas Technologies, Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, ChromaDB, Prompt Engineering, TensorFlow</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, MLflow</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=939926fb494cbe2c</t>
+          <t>https://www.indeed.com/viewjob?jk=a870d0f9729074bc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Engineer I</t>
+          <t>Senior Applied AI-Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FedEx Dataworks</t>
+          <t>Atlas Technologies, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Azure ML, Docker</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, MLflow</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,32 +659,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ccd4f80fb807bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=3d1bc3997769d78a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Platform Engineer/DevOp</t>
+          <t>Senior Applied AI-Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Atlas Technologies, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, Gemini, BigQuery, MLflow, Docker, Kubernetes, CI/CD, Jenkins</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, MLflow</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,102 +694,102 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c13abcae168f92</t>
+          <t>https://www.indeed.com/viewjob?jk=069fdf3c0cc292f9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Salesforce Developer with python-5</t>
+          <t>Senior Applied AI-Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Atlas Technologies, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Redshift, BigQuery, FastAPI, Snowflake, Databricks, BigQuery, Redshift</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, MLflow</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40fe46976f1c74ae</t>
+          <t>https://www.indeed.com/viewjob?jk=d3e8f5208c65efdb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Salesforce Developer with python-5</t>
+          <t>Senior Applied AI-Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Atlas Technologies, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Redshift, BigQuery, FastAPI, Snowflake, Databricks, BigQuery, Redshift</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, MLflow</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5bd4fe37ee6739a</t>
+          <t>https://www.indeed.com/viewjob?jk=a7ee238a8315a4cf</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Applied AI-Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Formlabs</t>
+          <t>Atlas Technologies, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Dataflow, Kubernetes, AKS, CI/CD, Git, Snowflake, Databricks</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, MLflow</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,32 +799,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e8e3bb316c3ab91</t>
+          <t>https://www.indeed.com/viewjob?jk=c0603ce9d8b53356</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Engineers</t>
+          <t>Senior Applied AI-Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Atlas Technologies, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, TensorFlow, PyTorch, scikit-learn</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, MLflow</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,32 +834,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=910c166b141fa129</t>
+          <t>https://www.indeed.com/viewjob?jk=e76719ea82301961</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer (Remote)</t>
+          <t>Senior Applied AI-Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Revenue Management Solutions</t>
+          <t>Atlas Technologies, Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, S3, Docker, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, MLflow</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,32 +869,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83625117c0bb978</t>
+          <t>https://www.indeed.com/viewjob?jk=5ff023a0de1350a1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Architect</t>
+          <t>Senior Applied AI-Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MojoTech</t>
+          <t>Atlas Technologies, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, AWS SageMaker, S3, Glue, Redshift, Kinesis, CI/CD, Git, Snowflake</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, MLflow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,32 +904,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4183923fb92626d</t>
+          <t>https://www.indeed.com/viewjob?jk=d3e02ed6797e3a94</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer - Experienced</t>
+          <t>Senior Applied AI-Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Richmond</t>
+          <t>Atlas Technologies, Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, S3, EC2, Docker, CI/CD, Terraform, Git</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, MLflow</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,32 +939,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ea0ba520f11fee7</t>
+          <t>https://www.indeed.com/viewjob?jk=bdbc66fdd0bbda12</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Senior Applied AI-Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Atlas Technologies, Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, scikit-learn, Docker, Kubernetes, Git, Kafka, PostgreSQL, Python</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, MLflow</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -974,32 +974,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a57b9b0b5d74551c</t>
+          <t>https://www.indeed.com/viewjob?jk=44c4a205f2636ada</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Senior Applied AI-Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Atlas Technologies, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, scikit-learn, Docker, Kubernetes, Git, Kafka, PostgreSQL, Python</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, MLflow</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,24 +1009,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d2567da3c97e0c2</t>
+          <t>https://www.indeed.com/viewjob?jk=2e62df056134e325</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - CTO innovations</t>
+          <t>Senior Applied AI-Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Atlas Technologies, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, OpenCV, Git, Snowflake, PySpark</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, MLflow</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1044,24 +1044,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb6bdbcc89b8901</t>
+          <t>https://www.indeed.com/viewjob?jk=d85ec9bde0060fac</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Data</t>
+          <t>Senior Applied AI-Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Atlas Technologies, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Jenkins, Terraform, Git, Snowflake, Databricks, MongoDB, Cassandra</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, MLflow</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,67 +1079,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b28eca491f11ed83</t>
+          <t>https://www.indeed.com/viewjob?jk=62da6b12ac3cb357</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GenAI Engineer-4</t>
+          <t>Senior Applied AI-Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Atlas Technologies, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, FAISS, Pinecone, ChromaDB</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, MLflow</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1f60dba5f2df86</t>
+          <t>https://www.indeed.com/viewjob?jk=d13fb35b9c83b26c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Applied AI-Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Solventum</t>
+          <t>Atlas Technologies, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, PyTorch, scikit-learn, MLflow, Docker, Kubernetes, CI/CD, Git, Python</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, MLflow</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1149,32 +1149,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2abeb02a0e515f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=74ea6078ac856be7</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior Applied AI-Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Armstrong World Industries</t>
+          <t>Atlas Technologies, Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lancaster, PA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, scikit-learn, Databricks, Tableau, Power BI, Python</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, MLflow</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1184,67 +1184,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b81c606945103730</t>
+          <t>https://www.indeed.com/viewjob?jk=d8cc14c714048d2e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Senior Applied AI-Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Magpie Health Analytics</t>
+          <t>Atlas Technologies, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, LLaMA, Hugging Face, S3, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, MLflow</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac90bdaf0b4a9199</t>
+          <t>https://www.indeed.com/viewjob?jk=ff642be30e786266</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MTS 1, Software Engineer</t>
+          <t>Senior Applied AI-Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Atlas Technologies, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Docker, Git, Kafka, Hadoop, MongoDB, Cassandra, Python</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, MLflow</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1254,32 +1254,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b54fe6ade52e7b03</t>
+          <t>https://www.indeed.com/viewjob?jk=e8bd90ec4c640187</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Integration Analyst</t>
+          <t>Senior Applied AI-Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>STP</t>
+          <t>Atlas Technologies, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Synapse, Data Lake, Dataflow, CI/CD, Git, PySpark, Tableau, Power BI</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, MLflow</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1289,67 +1289,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b236860653562b</t>
+          <t>https://www.indeed.com/viewjob?jk=43536b7e683f6ed5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cloud &amp; Security Engineer</t>
+          <t>Senior Applied AI-Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Novacis Digital</t>
+          <t>Atlas Technologies, Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, MLflow</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c2798550649837e</t>
+          <t>https://www.indeed.com/viewjob?jk=25fec72a9822832b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI &amp; Data Science Developer</t>
+          <t>Senior Applied AI-Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Itlize Global LLC</t>
+          <t>Atlas Technologies, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hugging Face, TensorFlow, PyTorch, scikit-learn, FastAPI, Docker, Git, Python, SQL, R</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, MLflow</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1359,32 +1359,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b73ed70c1781a16</t>
+          <t>https://www.indeed.com/viewjob?jk=0682f57301df868e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Applied AI-Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Evolent</t>
+          <t>Atlas Technologies, Inc.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, MLflow</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1394,32 +1394,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ac2a98b1400be6</t>
+          <t>https://www.indeed.com/viewjob?jk=89de84671e88afec</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Hadoop</t>
+          <t>Senior Applied AI-Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Atlas Technologies, Inc.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Databricks, Kafka, Hadoop, NoSQL, Python, SQL, R</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, MLflow</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1429,32 +1429,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2948fbe9d2340fca</t>
+          <t>https://www.indeed.com/viewjob?jk=aea28303ff1fc375</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Applied AI-Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FocusKPI Inc.</t>
+          <t>Atlas Technologies, Inc.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, CI/CD, Snowflake, BigQuery, Redshift, Python, SQL, R, Java</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, MLflow</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1464,32 +1464,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f951e4e29fe69c66</t>
+          <t>https://www.indeed.com/viewjob?jk=57a2435b97856be4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MTS 1, Software Engineer</t>
+          <t>Senior Applied AI-Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Atlas Technologies, Inc.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kubernetes, CI/CD, Jenkins, Git, Kafka, MongoDB, NoSQL, Python, SQL, R</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, MLflow</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1499,32 +1499,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98bd8d73e2e92638</t>
+          <t>https://www.indeed.com/viewjob?jk=c5469013f8b0e4fb</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Product Software Engineer - AI Quality Engineering</t>
+          <t>Senior Applied AI-Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Wolters Kluwer</t>
+          <t>Atlas Technologies, Inc.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cape Girardeau, MO, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Pinecone, Docker, Kubernetes, CI/CD, Git, Python</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, MLflow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1534,32 +1534,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03692da1102d4d71</t>
+          <t>https://www.indeed.com/viewjob?jk=9c1519d9373d950a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data/AI Engineering</t>
+          <t>Senior Applied AI-Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Atlas Technologies, Inc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, CI/CD, Snowflake, Databricks, Kafka, Python, SQL, R, Java</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, MLflow</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1569,32 +1569,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f18e8940a4968b5</t>
+          <t>https://www.indeed.com/viewjob?jk=93c7c93ebe98dbf5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Engineer Sr</t>
+          <t>Senior Applied AI-Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bobcat</t>
+          <t>Atlas Technologies, Inc.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>West Fargo, ND, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, Hugging Face, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, MLflow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1604,32 +1604,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd32f6cd28f44b63</t>
+          <t>https://www.indeed.com/viewjob?jk=00ecf7a120fc3bac</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Senior Digital Banking Full Stack Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>First Tech Federal Credit Union</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chelmsford, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, FastAPI, Kubernetes, CI/CD, Git, Kafka, Python, R</t>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, SQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1639,32 +1639,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a533234b88d7c22a</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8a5dfa62a0d990</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI/ML Engineer -Agentic Private Bank Engineer, Senior Associate</t>
+          <t>Senior Digital Banking Full Stack Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>First Tech Federal Credit Union</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Hillsboro, OR, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, SQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1674,32 +1674,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=469baae0b7223b65</t>
+          <t>https://www.indeed.com/viewjob?jk=e7da1ea0ad17289e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Digital Banking Full Stack Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>First Tech Federal Credit Union</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL, SQL, R</t>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, SQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1709,32 +1709,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=389bda3afea947e0</t>
+          <t>https://www.indeed.com/viewjob?jk=c6fffdae1534f271</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Analytics Bootcamp Instructor (Part-Time / Contract), Multiple Subject Areas</t>
+          <t>Senior Digital Banking Full Stack Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Manhattan` Institute of Management</t>
+          <t>First Tech Federal Credit Union</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Data Scientist, scikit-learn, Keras, Git, PostgreSQL, Tableau, Power BI, Matplotlib, Seaborn, Python</t>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, SQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1744,32 +1744,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d34f3def9e2a825</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0564e4c963eeaa</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer III - ETL</t>
+          <t>Senior Digital Banking Full Stack Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>First Tech Federal Credit Union</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Rocklin, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Databricks, NoSQL, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, SQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1779,32 +1779,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48b8fa5e3eb4a90c</t>
+          <t>https://www.indeed.com/viewjob?jk=64568d42f66cc32c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer III - MLOps</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, R, Java</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1814,32 +1814,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8480ac6de047118</t>
+          <t>https://www.indeed.com/viewjob?jk=7348aaf9ea0dffed</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (PACS) - Full Time - Remote</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Experity</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1849,32 +1849,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdcbd7a94e077e55</t>
+          <t>https://www.indeed.com/viewjob?jk=8839314f6759c131</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Credit Risk</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, Keras, NLTK, Git, Python, SQL, R, Java</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1884,32 +1884,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=110f6e88460f2fd4</t>
+          <t>https://www.indeed.com/viewjob?jk=2db021d4795c74b4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Snowflake</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Cortex, S3, Git, Snowflake, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1919,32 +1919,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46451a72c65c2e35</t>
+          <t>https://www.indeed.com/viewjob?jk=d0feddabdba27405</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Sr. Data Scientist Job</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Armstrong World Industries</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Lancaster, PA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, Kubernetes, Git, Python, R</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, scikit-learn, Databricks, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1954,32 +1954,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2280dcd14868a00</t>
+          <t>https://www.indeed.com/viewjob?jk=6bfe23127b82b76c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Full-Stack/UI Senior Software Engineer - 26375</t>
+          <t>Full-Stack Engineer 4 (Java, Kafka, AWS)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Enverus</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Generative AI, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b19e7c7f80c8e47</t>
+          <t>https://www.indeed.com/viewjob?jk=246675a88211c8be</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
+          <t>Senior AI Full Stack Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Centric Software</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Campbell, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Jenkins, Git, NoSQL, Python, SQL, R, Java, C++, Scala, Optimization</t>
+          <t>AI Engineer, Generative AI, RAG, LLaMA, Docker, Kubernetes, CI/CD, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2024,67 +2024,67 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcb4225374ff5e96</t>
+          <t>https://www.indeed.com/viewjob?jk=5f4305a1e207c61a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java Full Stack)</t>
+          <t>Automation Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Optimum</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethpage, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, CI/CD, Git, Kafka, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Prompt Engineering, BigQuery, Docker, CI/CD, Git, BigQuery, Kafka, Python</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f87cbf3c6196383</t>
+          <t>https://www.indeed.com/viewjob?jk=f6d4c3963dc4d046</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Full Stack Developer — Global Health &amp; AI (REMOTE ROLE)</t>
+          <t>Full-Stack Engineer 4</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2094,32 +2094,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4aba9a4812914d4</t>
+          <t>https://www.indeed.com/viewjob?jk=2a0e6e498f727e5e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Full stack software engineer</t>
+          <t>Full-Stack Engineer 4 (SQL Server DBA)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2129,32 +2129,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fef7970decc80bb</t>
+          <t>https://www.indeed.com/viewjob?jk=f393fa8d32e16893</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Enterprise AI Security Engineer</t>
+          <t>Full-stack Engineer 4 (Java, Python, JavaScript)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RAG, Athena, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2164,32 +2164,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72bb777e6045e6c1</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6e40de4c01a38c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>Senior Product Software Engineer - AI Quality Engineering</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>OnX</t>
+          <t>Wolters Kluwer</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Cape Girardeau, MO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, Terraform, Git, PostgreSQL, MySQL, Python, SQL, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Pinecone, Docker, Kubernetes, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2199,32 +2199,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3243df3687a8dab</t>
+          <t>https://www.indeed.com/viewjob?jk=a6fa90aef0cf777f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>Senior DBA II</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Onx Homes</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, Terraform, Git, PostgreSQL, MySQL, Python, SQL, R, Scala</t>
+          <t>CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2234,32 +2234,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=977ace2d9d1e2ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=aa3a48755605f28e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>Senior DBA II</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>OnX</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, Terraform, Git, PostgreSQL, MySQL, Python, SQL, R, Scala</t>
+          <t>CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2269,32 +2269,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f134c41ea48f5e3a</t>
+          <t>https://www.indeed.com/viewjob?jk=68f070fab73c645f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>Senior DBA II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>OnX</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, Terraform, Git, PostgreSQL, MySQL, Python, SQL, R, Scala</t>
+          <t>CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2304,32 +2304,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23bf19bd58d90737</t>
+          <t>https://www.indeed.com/viewjob?jk=acdebbbdc22b8477</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Senior DBA II</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RAG, Kafka, Hadoop, Cassandra, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2339,32 +2339,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c365530d5e90342</t>
+          <t>https://www.indeed.com/viewjob?jk=543fff0177376c1b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior AI Scientist - Mid-Market Intelligence</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Xcel Energy</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Amarillo, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, PyTorch, scikit-learn, PySpark, Python, SQL, R, Optimization</t>
+          <t>RAG, Data Lake, CI/CD, Terraform, Git, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2374,32 +2374,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba2af9212e90bcd6</t>
+          <t>https://www.indeed.com/viewjob?jk=25c51b626d77472c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Planet DDS</t>
+          <t>Xcel Energy</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Eau Claire, WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, Data Lake, CI/CD, Terraform, Git, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2409,32 +2409,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4ee5c63653453c7</t>
+          <t>https://www.indeed.com/viewjob?jk=ea336bd03fc8adb1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java/AWS</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Xcel Energy</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Terraform, Git, Kafka, R, Java, Scala, Optimization</t>
+          <t>RAG, Data Lake, CI/CD, Terraform, Git, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2444,32 +2444,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d94cf9403ac15237</t>
+          <t>https://www.indeed.com/viewjob?jk=b15a9d448062578a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Capgemini Engineering</t>
+          <t>Xcel Energy</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, Data Lake, CI/CD, Terraform, Git, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2479,32 +2479,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0b81c8fb8e23afc</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c99bf247866440</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Software Engineer - Enablement</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Acima Leasing</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RAG, MLflow, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
+          <t>Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2514,32 +2514,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7d27339ccef1f0</t>
+          <t>https://www.indeed.com/viewjob?jk=3810a31823a2bca2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>AI Data Engineer III</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Boston Scientific</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arden Hills, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RAG, MLflow, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9b09df58bdb608c</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b56cbb884ad319</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior AI Scientist - Consumer Fraud Risk</t>
+          <t>Data Scientist Senior</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Apache Airflow, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, Docker, Terraform, Hadoop, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2584,42 +2584,672 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40491952636aaf86</t>
+          <t>https://www.indeed.com/viewjob?jk=f119960c891ab5ce</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Sr. Systems Engineer - Manufacturing Plant Floor Systems</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Oshkosh Corporation</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, CI/CD, Git, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a23c424bcc5003c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer Graduate (E-Commerce Knowledge Graph) - 2027 Start</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Hadoop, Python, R, Java, C++</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f4857ddc9e1a382</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Machine Learning Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ImagineSoftware</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, S3, EC2, MLflow, CI/CD, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a5dc68f6ea04512</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>AI Engineer 4 (MLX, Agentic AI, Gen AI platform Services)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
         <v>10</v>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Data Scientist, Kafka, Hadoop, NoSQL, Python, SQL, R, Java, C++</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e101436eff3e3887</t>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, PyTorch, Python, R, Java, C++, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d5fd32451813431</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Technical Cost Analyst, IT Cost Transparency &amp; Optimization</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=23dcc441cb3257d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Technical Cost Analyst, IT Cost Transparency &amp; Optimization</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42441b3c3603454b</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Technical Cost Analyst, IT Cost Transparency &amp; Optimization</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b50e4c3c54942a87</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Technical Cost Analyst, IT Cost Transparency &amp; Optimization</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dfafccebd91099d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Technical Cost Analyst, IT Cost Transparency &amp; Optimization</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81238827afeba0d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Technical Cost Analyst, IT Cost Transparency &amp; Optimization</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=684d0f20adeab8ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Technical Cost Analyst, IT Cost Transparency &amp; Optimization</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2510c022d884b9fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Agentic AI Software Engineer - Equipment Data Analytics</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>KLA</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Milpitas, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, NoSQL, Python, SQL, R, Java, C++, Scala</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ef893852cbca60c</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Software Engineer, Full Stack, Level 4</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aefcbc065ee034f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer (Data &amp; Integrations Engineering)</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Cedar INC</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>RAG, Apache Airflow, CI/CD, Snowflake, Kafka, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1a64073f77de1fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Data Scientist - AI and Data Science Engineer I</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, MLflow, Git, Databricks, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b2c8f936ee1345ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Data Scientist - AI and Data Science Engineer I</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, MLflow, Git, Databricks, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e77a9d2c70b69ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ImagineSoftware</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a1c59d5f8bcc743</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Platform Engineer - DevOps Specialist L2</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Generative AI, PyTorch, EC2, Docker, Kubernetes, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0bfb453a1b7cdc6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Epsilon</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Hadoop, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31e7731f1f9f1fba</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-10-08.xlsx
+++ b/daily_matches/job_matches_2026-10-08.xlsx
@@ -456,25 +456,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Scientist (LAP)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Louisville, KY, USA USA</t>
+          <t>Eden Prairie, MN, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, scikit-learn, BigQuery, Dataflow, FastAPI, Git, BigQuery</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,32 +484,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de9afd3ca646a72</t>
+          <t>https://www.indeed.com/viewjob?jk=6ecc8f399660dece</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer - Remote</t>
+          <t>AI-Native Full Stack Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>DataArt</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, scikit-learn, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,24 +519,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8277a6ad907dfe29</t>
+          <t>https://www.indeed.com/viewjob?jk=89948ae133bdb918</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>Irvine, CA, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -544,7 +544,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Synapse, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, scikit-learn, Keras, Docker, Kubernetes, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,32 +554,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e3c1554c10248b1</t>
+          <t>https://www.indeed.com/viewjob?jk=941ac528d3de9bd2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Full stack Software Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Columbus, OH, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, RAG, GPT-4, LLaMA, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, Git</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, CI/CD, Terraform, Git, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,24 +589,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3590af910c1daec6</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb5ca6a9acf3091</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr Associate AI Full stack Software Engineer</t>
+          <t>Senior Software Engineer I (Data Pipelines)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Wpromote, LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Columbus, OH, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, GPT-4, LLaMA, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, Git</t>
+          <t>RAG, BigQuery, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,32 +624,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d80cd7acfdcd7bbd</t>
+          <t>https://www.indeed.com/viewjob?jk=77f88462ba46b951</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine (AI/ML) Learning Engineer</t>
+          <t>AI Web Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Living Spaces</t>
+          <t>Infinity Optic Network</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>La Mirada, CA, USA USA</t>
+          <t>Bountiful, UT, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, TensorFlow, PyTorch, scikit-learn, Azure ML, BigQuery, Databricks, BigQuery</t>
+          <t>Docker, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,32 +659,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cddf643063b08655</t>
+          <t>https://www.indeed.com/viewjob?jk=15b1fd07aaa46d72</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 1</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Clinical Ink</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Snowflake, Databricks</t>
+          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,32 +694,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b3948f463d0e34</t>
+          <t>https://www.indeed.com/viewjob?jk=b281122b47c7d487</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer-Xumo</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irvine, CA, USA USA</t>
+          <t>Reston, VA, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, BigQuery, Git, BigQuery, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Git, Databricks, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,24 +729,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d075be1566febf4</t>
+          <t>https://www.indeed.com/viewjob?jk=7aec8d989d23632c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ML Ops Technical Specialist - DevOps, Python</t>
+          <t>Software Engineer, Machine Learning Platform - MDX</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -754,7 +754,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Data Scientist, RAG, LLaMA, TensorFlow, PyTorch, MLflow, Apache Airflow, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,32 +764,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db384956af70feec</t>
+          <t>https://www.indeed.com/viewjob?jk=0eaaebd5168da317</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. GenAI Engineer</t>
+          <t>Full Stack Developer - Python/Flask/FastAPI &amp; LLM &amp; React</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Finbott</t>
+          <t>RLink Solutions LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, Hadoop, Tableau, Python, SQL, R, Java</t>
+          <t>LangChain, RAG, LLaMA, Copilot, Prompt Engineering, FastAPI, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,24 +799,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00517b64222c070</t>
+          <t>https://www.indeed.com/viewjob?jk=f57146c20a302931</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Quant Analytics Senior associate - Card Data Analaytics</t>
+          <t>AI Engineer - Go To Market</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wilmington, DE, USA USA</t>
+          <t>Temple Terrace, FL, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -824,7 +824,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Git, Hadoop, Tableau, Python, SQL, R, Optimization</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, GCP Vertex AI, Docker, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,24 +834,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8259102faba5e33e</t>
+          <t>https://www.indeed.com/viewjob?jk=d24b3f955e2406d6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, CMS</t>
+          <t>AI Frameworks Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Intel Corporation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nashville, TN, USA USA</t>
+          <t>Santa Clara, CA, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -859,7 +859,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, Git, Kafka, R, Java, Scala</t>
+          <t>TensorFlow, PyTorch, Dataflow, Docker, Kubernetes, Git, Python, R, C++, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,24 +869,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd24c1cc7773c508</t>
+          <t>https://www.indeed.com/viewjob?jk=44a21e85729d8138</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Data Validation Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Xcel Energy</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denver, CO, USA USA</t>
+          <t>Reston, VA, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Terraform, Git, Databricks, Python, SQL, R, Scala</t>
+          <t>AI Engineer, RAG, MLflow, CI/CD, GitHub Actions, Terraform, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,32 +904,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b919d7fa31ebc26</t>
+          <t>https://www.indeed.com/viewjob?jk=3eb22b319ea013fb</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data/ML Engineer</t>
+          <t>Full Stack Developer III</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>BAM Technologies, LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Princeton, NJ, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, CI/CD, Terraform, Databricks, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,24 +939,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d1dcb506d9ce871</t>
+          <t>https://www.indeed.com/viewjob?jk=12b4ba48e48f905c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VIE - Software Engineer (based in Miami)</t>
+          <t>AI Solutions Engineer, Advancement</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pelico</t>
+          <t>Babson College</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Miami, FL, USA USA</t>
+          <t>Wellesley, MA, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -964,7 +964,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, PostgreSQL, MongoDB, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Prompt Engineering, Tableau, Python, SQL, R, Java, C++, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -974,24 +974,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b64e32ec1fb240</t>
+          <t>https://www.indeed.com/viewjob?jk=da0d1913dae63afb</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Machine Learning Infrastructure Engineer, Recommendations and Search</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Curant Health Georgia LLC</t>
+          <t>TikTok USDS JV</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Smyrna, GA, USA USA</t>
+          <t>San Jose, CA, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -999,7 +999,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Synapse, CI/CD, Snowflake, Databricks, SQL, R, Scala, Optimization</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, R, Java, C++, Scala, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,24 +1009,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f2fb1b8f4b0f0b</t>
+          <t>https://www.indeed.com/viewjob?jk=bf2d3c7782147fcb</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Computer Vision and Automation Specialist</t>
+          <t>Senior Forward Deployed Engineer (10569)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kubota Manufacturing of America</t>
+          <t>Extreme Networks</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Gainesville, GA, USA USA</t>
+          <t>Seattle, WA, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Copilot, PyTorch, OpenCV, YOLO, Docker, Git, Python, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, C++, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1044,24 +1044,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9022b92c09ad6558</t>
+          <t>https://www.indeed.com/viewjob?jk=b270501d0db13e47</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Operational Analytics</t>
+          <t>Machine Learning Infrastructure Engineer, Recommendations and Search</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>TikTok USDS JV</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hartford, CT, USA USA</t>
+          <t>Seattle, WA, USA USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Scala</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, R, Java, C++, Scala, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,32 +1079,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdb3290ccce5b48b</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c6fe8a4f28a31e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Software Engineer, Machine Learning Platform - Gen AI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tekmetric</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Houston, TX, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Kubernetes, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1114,24 +1114,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02656011a059ed46</t>
+          <t>https://www.indeed.com/viewjob?jk=c080695c3be29772</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Embedded AI Tools Engineer</t>
+          <t>GenAI Engineer expert / Pharma ERP(Raritan, NJ .Hybrid)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Analog Devices</t>
+          <t>COMPEST SOLUTIONS INDIA PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wilmington, MA, USA USA</t>
+          <t>Raritan, NJ, USA USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, CI/CD, Git, Python, R, C++, Optimization</t>
+          <t>AI Engineer, Generative AI, RAG, CI/CD, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1149,24 +1149,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec84e1326b70c68b</t>
+          <t>https://www.indeed.com/viewjob?jk=ddd37e28b069e4aa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>American Arbitration Association</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Milpitas, CA, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Tableau, Python, SQL, R, Java, C++</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1184,24 +1184,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17e12cb133cd0110</t>
+          <t>https://www.indeed.com/viewjob?jk=ec9097d6ee7df68c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SBC SR DATA &amp; AI SOLUTIONS ENG</t>
+          <t>Senior AI Analyst, People Digital Solutions</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Stanford Health Care</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Tableau, Power BI, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Generative AI, Prompt Engineering, Git, Tableau, Power BI, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1219,24 +1219,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c8e123b28065b9</t>
+          <t>https://www.indeed.com/viewjob?jk=442e554894a24297</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior AI Analyst, People Digital Solutions</t>
+          <t>Azure Platform Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Generative AI, Prompt Engineering, Git, Tableau, Power BI, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Terraform, Git, R, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1254,24 +1254,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31895eb722198e44</t>
+          <t>https://www.indeed.com/viewjob?jk=5465f937ef830c41</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Stage - Ingénieur/e Intelligence Artificielle (RAG)</t>
+          <t>AI Creative Technologist</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dassault Aviation</t>
+          <t>Hill's Pet Nutrition</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saint Cloud, MN, USA USA</t>
+          <t>Overland Park, KS, USA USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, FAISS, ChromaDB, Prompt Engineering, FastAPI, Python, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1289,24 +1289,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3e674dc99bf25e6</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c4622492b9edf6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior AI Analyst, People Digital Solutions</t>
+          <t>Enterprise Software Engineer II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Dartmouth College</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bellevue, WA, USA USA</t>
+          <t>Hanover, NH, USA USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Generative AI, Prompt Engineering, Git, Tableau, Power BI, SQL, R, Scala, Optimization</t>
+          <t>Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e6a749467f299e6</t>
+          <t>https://www.indeed.com/viewjob?jk=147e1a8f49587d0f</t>
         </is>
       </c>
     </row>
